--- a/WorkBot/refactor/data/orders/Webstaurant/Webstaurant_Triphammer_2025-10-10.xlsx
+++ b/WorkBot/refactor/data/orders/Webstaurant/Webstaurant_Triphammer_2025-10-10.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,6 +467,33 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>20.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>104APRICOT28</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Apricot - Dried</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>128.49</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>256.98</t>
         </is>
       </c>
     </row>
